--- a/app/data/catalogues/SemSac_lieux_total_geocode.xlsx
+++ b/app/data/catalogues/SemSac_lieux_total_geocode.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="SemSac lieux total geocodes 202" r:id="rId3" sheetId="1"/>
+    <sheet name="SemSac_lieux_total_geocode_2026" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -17755,7 +17755,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Rieutort-de-Randon</t>
+          <t>Monts-de-Randon</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -20160,7 +20160,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Antraigues-sur-Volane (Ardèche, France)</t>
+          <t>Vallées-d'Antraigues-Asperjoc (Ardèche, France)</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -20175,7 +20175,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Antraigues-sur-Volane</t>
+          <t>Vallées-d'Antraigues-Asperjoc</t>
         </is>
       </c>
       <c r="E691"/>
@@ -20882,7 +20882,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Ch芒teauneuf-de-Vernoux (Ardèche, France)</t>
+          <t>Châteauneuf-de-Vernoux (Ardèche, France)</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -20897,7 +20897,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Ch芒teauneuf-de-Vernoux</t>
+          <t>Châteauneuf-de-Vernoux</t>
         </is>
       </c>
       <c r="E710"/>
@@ -22516,7 +22516,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>Saint-脡tienne-de-Fontbellon (Ardèche, France)</t>
+          <t>Saint-Étienne-de-Fontbellon (Ardèche, France)</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Saint-脡tienne-de-Fontbellon</t>
+          <t>Saint-Étienne-de-Fontbellon</t>
         </is>
       </c>
       <c r="E753"/>
@@ -31256,7 +31256,7 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>Saint-Beno卯t (Aude, France)</t>
+          <t>Saint-Benoît (Aude, France)</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -31271,7 +31271,7 @@
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>Saint-Beno卯t</t>
+          <t>Saint-Benoît</t>
         </is>
       </c>
       <c r="E983"/>
@@ -33042,7 +33042,7 @@
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>Brousse-le-Ch芒teau (Aveyron, France)</t>
+          <t>Brousse-le-Château (Aveyron, France)</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
@@ -33057,7 +33057,7 @@
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>Brousse-le-Ch芒teau</t>
+          <t>Brousse-le-Château</t>
         </is>
       </c>
       <c r="E1030"/>
@@ -34220,7 +34220,7 @@
     <row r="1061">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>Laissac-Sévérac l'脡glise (Aveyron, France)</t>
+          <t>Laissac-Sévérac l'Église (Aveyron, France)</t>
         </is>
       </c>
       <c r="B1061" t="inlineStr">
@@ -34235,7 +34235,7 @@
       </c>
       <c r="D1061" t="inlineStr">
         <is>
-          <t>Laissac-Sévérac l'脡glise</t>
+          <t>Laissac-Sévérac l'Église</t>
         </is>
       </c>
       <c r="E1061"/>
@@ -35208,7 +35208,7 @@
     <row r="1087">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>Onet-le-Ch芒teau (Aveyron, France)</t>
+          <t>Onet-le-Château (Aveyron, France)</t>
         </is>
       </c>
       <c r="B1087" t="inlineStr">
@@ -35223,7 +35223,7 @@
       </c>
       <c r="D1087" t="inlineStr">
         <is>
-          <t>Onet-le-Ch芒teau</t>
+          <t>Onet-le-Château</t>
         </is>
       </c>
       <c r="E1087"/>
@@ -35930,7 +35930,7 @@
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>Saint-Georges-de-Luzen莽on (Aveyron, France)</t>
+          <t>Saint-Georges-de-Luzençon (Aveyron, France)</t>
         </is>
       </c>
       <c r="B1106" t="inlineStr">
@@ -35945,7 +35945,7 @@
       </c>
       <c r="D1106" t="inlineStr">
         <is>
-          <t>Saint-Georges-de-Luzen莽on</t>
+          <t>Saint-Georges-de-Luzençon</t>
         </is>
       </c>
       <c r="E1106"/>
@@ -37374,7 +37374,7 @@
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>Auriac-l'脡glise (Cantal, France)</t>
+          <t>Auriac-l'Église (Cantal, France)</t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="D1144" t="inlineStr">
         <is>
-          <t>Auriac-l'脡glise</t>
+          <t>Auriac-l'Église</t>
         </is>
       </c>
       <c r="E1144"/>
@@ -38894,7 +38894,7 @@
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>Bréau-et-Salagosse (Gard, France)</t>
+          <t>Bréau-Mars (Gard, France)</t>
         </is>
       </c>
       <c r="B1184" t="inlineStr">
@@ -40756,7 +40756,7 @@
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>N卯mes (Gard, France)</t>
+          <t>Nîmes (Gard, France)</t>
         </is>
       </c>
       <c r="B1233" t="inlineStr">
@@ -40771,7 +40771,7 @@
       </c>
       <c r="D1233" t="inlineStr">
         <is>
-          <t>N卯mes</t>
+          <t>Nîmes</t>
         </is>
       </c>
       <c r="E1233"/>
@@ -48090,7 +48090,7 @@
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>Lagr芒ce-Dieu (Haute-Garonne, France)</t>
+          <t>Lagrâce-Dieu (Haute-Garonne, France)</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
@@ -48105,7 +48105,7 @@
       </c>
       <c r="D1426" t="inlineStr">
         <is>
-          <t>Lagr芒ce-Dieu</t>
+          <t>Lagrâce-Dieu</t>
         </is>
       </c>
       <c r="E1426"/>
@@ -51814,7 +51814,7 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>Saint-Béat (Haute-Garonne, France)</t>
+          <t>Saint-Béat-Lez (Haute-Garonne, France)</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
@@ -51829,7 +51829,7 @@
       </c>
       <c r="D1524" t="inlineStr">
         <is>
-          <t>Saint-Béat</t>
+          <t>Saint-Béat-Lez</t>
         </is>
       </c>
       <c r="E1524"/>
@@ -55120,7 +55120,7 @@
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>Escorneb艙uf (Gers, France)</t>
+          <t>Escornebœuf (Gers, France)</t>
         </is>
       </c>
       <c r="B1611" t="inlineStr">
@@ -55135,7 +55135,7 @@
       </c>
       <c r="D1611" t="inlineStr">
         <is>
-          <t>Escorneb艙uf</t>
+          <t>Escornebœuf</t>
         </is>
       </c>
       <c r="E1611"/>
@@ -56108,7 +56108,7 @@
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>Laura毛t (Gers, France)</t>
+          <t>Lauraët (Gers, France)</t>
         </is>
       </c>
       <c r="B1637" t="inlineStr">
@@ -56123,7 +56123,7 @@
       </c>
       <c r="D1637" t="inlineStr">
         <is>
-          <t>Laura毛t</t>
+          <t>Lauraët</t>
         </is>
       </c>
       <c r="E1637"/>
@@ -57210,7 +57210,7 @@
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>Montpézat (Gers, France)</t>
+          <t>Montpezat (Gers, France)</t>
         </is>
       </c>
       <c r="B1666" t="inlineStr">
@@ -57225,7 +57225,7 @@
       </c>
       <c r="D1666" t="inlineStr">
         <is>
-          <t>Montpézat</t>
+          <t>Montpezat</t>
         </is>
       </c>
       <c r="E1666"/>
@@ -62454,7 +62454,7 @@
     <row r="1804">
       <c r="A1804" t="inlineStr">
         <is>
-          <t>Nézignan-l'脡v锚que (Hérault, France)</t>
+          <t>Nézignan-l'Évêque (Hérault, France)</t>
         </is>
       </c>
       <c r="B1804" t="inlineStr">
@@ -62469,7 +62469,7 @@
       </c>
       <c r="D1804" t="inlineStr">
         <is>
-          <t>Nézignan-l'脡v锚que</t>
+          <t>Nézignan-l'Évêque</t>
         </is>
       </c>
       <c r="E1804"/>
@@ -65722,7 +65722,7 @@
     <row r="1890">
       <c r="A1890" t="inlineStr">
         <is>
-          <t>Lavo没te-Chilhac (Haute-Loire, France)</t>
+          <t>Lavoûte-Chilhac (Haute-Loire, France)</t>
         </is>
       </c>
       <c r="B1890" t="inlineStr">
@@ -65737,7 +65737,7 @@
       </c>
       <c r="D1890" t="inlineStr">
         <is>
-          <t>Lavo没te-Chilhac</t>
+          <t>Lavoûte-Chilhac</t>
         </is>
       </c>
       <c r="E1890"/>
@@ -65760,7 +65760,7 @@
     <row r="1891">
       <c r="A1891" t="inlineStr">
         <is>
-          <t>Lavo没te-sur-Loire (Haute-Loire, France)</t>
+          <t>Lavoûte-sur-Loire (Haute-Loire, France)</t>
         </is>
       </c>
       <c r="B1891" t="inlineStr">
@@ -65775,7 +65775,7 @@
       </c>
       <c r="D1891" t="inlineStr">
         <is>
-          <t>Lavo没te-sur-Loire</t>
+          <t>Lavoûte-sur-Loire</t>
         </is>
       </c>
       <c r="E1891"/>
@@ -65798,7 +65798,7 @@
     <row r="1892">
       <c r="A1892" t="inlineStr">
         <is>
-          <t>Merc艙ur (Haute-Loire, France)</t>
+          <t>Mercœur (Haute-Loire, France)</t>
         </is>
       </c>
       <c r="B1892" t="inlineStr">
@@ -65813,7 +65813,7 @@
       </c>
       <c r="D1892" t="inlineStr">
         <is>
-          <t>Merc艙ur</t>
+          <t>Mercœur</t>
         </is>
       </c>
       <c r="E1892"/>
@@ -66064,7 +66064,7 @@
     <row r="1899">
       <c r="A1899" t="inlineStr">
         <is>
-          <t>Saint-脡tienne-Lardeyrol (Haute-Loire, France)</t>
+          <t>Saint-Étienne-Lardeyrol (Haute-Loire, France)</t>
         </is>
       </c>
       <c r="B1899" t="inlineStr">
@@ -66079,7 +66079,7 @@
       </c>
       <c r="D1899" t="inlineStr">
         <is>
-          <t>Saint-脡tienne-Lardeyrol</t>
+          <t>Saint-Étienne-Lardeyrol</t>
         </is>
       </c>
       <c r="E1899"/>
@@ -72524,7 +72524,7 @@
     <row r="2069">
       <c r="A2069" t="inlineStr">
         <is>
-          <t>Chambon-le-Ch芒teau (Lozère, France)</t>
+          <t>Chambon-le-Château (Lozère, France)</t>
         </is>
       </c>
       <c r="B2069" t="inlineStr">
@@ -72539,7 +72539,7 @@
       </c>
       <c r="D2069" t="inlineStr">
         <is>
-          <t>Chambon-le-Ch芒teau</t>
+          <t>Chambon-le-Château</t>
         </is>
       </c>
       <c r="E2069"/>
@@ -73778,7 +73778,7 @@
     <row r="2102">
       <c r="A2102" t="inlineStr">
         <is>
-          <t>Sainte-Croix-Vallée-Fran莽aise (Lozère, France)</t>
+          <t>Sainte-Croix-Vallée-Française (Lozère, France)</t>
         </is>
       </c>
       <c r="B2102" t="inlineStr">
@@ -73793,7 +73793,7 @@
       </c>
       <c r="D2102" t="inlineStr">
         <is>
-          <t>Sainte-Croix-Vallée-Fran莽aise</t>
+          <t>Sainte-Croix-Vallée-Française</t>
         </is>
       </c>
       <c r="E2102"/>
@@ -73892,7 +73892,7 @@
     <row r="2105">
       <c r="A2105" t="inlineStr">
         <is>
-          <t>Saint-脡tienne-du-Valdonnez (Lozère, France)</t>
+          <t>Saint-Étienne-du-Valdonnez (Lozère, France)</t>
         </is>
       </c>
       <c r="B2105" t="inlineStr">
@@ -73907,7 +73907,7 @@
       </c>
       <c r="D2105" t="inlineStr">
         <is>
-          <t>Saint-脡tienne-du-Valdonnez</t>
+          <t>Saint-Étienne-du-Valdonnez</t>
         </is>
       </c>
       <c r="E2105"/>
@@ -73930,7 +73930,7 @@
     <row r="2106">
       <c r="A2106" t="inlineStr">
         <is>
-          <t>Saint-脡tienne-Vallée-Fran莽aise (Lozère, France)</t>
+          <t>Saint-Étienne-Vallée-Française (Lozère, France)</t>
         </is>
       </c>
       <c r="B2106" t="inlineStr">
@@ -73945,7 +73945,7 @@
       </c>
       <c r="D2106" t="inlineStr">
         <is>
-          <t>Saint-脡tienne-Vallée-Fran莽aise</t>
+          <t>Saint-Étienne-Vallée-Française</t>
         </is>
       </c>
       <c r="E2106"/>
@@ -76932,7 +76932,7 @@
     <row r="2185">
       <c r="A2185" t="inlineStr">
         <is>
-          <t>Lan莽on (Hautes-Pyrénées, France)</t>
+          <t>Lançon (Hautes-Pyrénées, France)</t>
         </is>
       </c>
       <c r="B2185" t="inlineStr">
@@ -76947,7 +76947,7 @@
       </c>
       <c r="D2185" t="inlineStr">
         <is>
-          <t>Lan莽on</t>
+          <t>Lançon</t>
         </is>
       </c>
       <c r="E2185"/>
@@ -78870,7 +78870,7 @@
     <row r="2236">
       <c r="A2236" t="inlineStr">
         <is>
-          <t>Trameza茂gues (Hautes-Pyrénées, France)</t>
+          <t>Tramezaïgues (Hautes-Pyrénées, France)</t>
         </is>
       </c>
       <c r="B2236" t="inlineStr">
@@ -78885,7 +78885,7 @@
       </c>
       <c r="D2236" t="inlineStr">
         <is>
-          <t>Trameza茂gues</t>
+          <t>Tramezaïgues</t>
         </is>
       </c>
       <c r="E2236"/>
@@ -78946,7 +78946,7 @@
     <row r="2238">
       <c r="A2238" t="inlineStr">
         <is>
-          <t>Trie-sur-Ba茂se (Hautes-Pyrénées, France)</t>
+          <t>Trie-sur-Baïse (Hautes-Pyrénées, France)</t>
         </is>
       </c>
       <c r="B2238" t="inlineStr">
@@ -78961,7 +78961,7 @@
       </c>
       <c r="D2238" t="inlineStr">
         <is>
-          <t>Trie-sur-Ba茂se</t>
+          <t>Trie-sur-Baïse</t>
         </is>
       </c>
       <c r="E2238"/>
@@ -79554,7 +79554,7 @@
     <row r="2254">
       <c r="A2254" t="inlineStr">
         <is>
-          <t>Montalba-le-Ch芒teau (Pyrénées-Orientales, France)</t>
+          <t>Montalba-le-Château (Pyrénées-Orientales, France)</t>
         </is>
       </c>
       <c r="B2254" t="inlineStr">
@@ -79569,7 +79569,7 @@
       </c>
       <c r="D2254" t="inlineStr">
         <is>
-          <t>Montalba-le-Ch芒teau</t>
+          <t>Montalba-le-Château</t>
         </is>
       </c>
       <c r="E2254"/>
@@ -83468,7 +83468,7 @@
     <row r="2357">
       <c r="A2357" t="inlineStr">
         <is>
-          <t>Roumégoux (Tarn, France)</t>
+          <t>Terre-de-Bancalié (Tarn, France)</t>
         </is>
       </c>
       <c r="B2357" t="inlineStr">
@@ -83483,7 +83483,7 @@
       </c>
       <c r="D2357" t="inlineStr">
         <is>
-          <t>Roumégoux</t>
+          <t>Terre-de-Bancalié</t>
         </is>
       </c>
       <c r="E2357"/>
@@ -83772,7 +83772,7 @@
     <row r="2365">
       <c r="A2365" t="inlineStr">
         <is>
-          <t>Sa茂x (Tarn, France)</t>
+          <t>Saïx (Tarn, France)</t>
         </is>
       </c>
       <c r="B2365" t="inlineStr">
@@ -83787,7 +83787,7 @@
       </c>
       <c r="D2365" t="inlineStr">
         <is>
-          <t>Sa茂x</t>
+          <t>Saïx</t>
         </is>
       </c>
       <c r="E2365"/>
@@ -86394,7 +86394,7 @@
     <row r="2434">
       <c r="A2434" t="inlineStr">
         <is>
-          <t>Lafran莽aise (Tarn-et-Garonne, France)</t>
+          <t>Lafrançaise (Tarn-et-Garonne, France)</t>
         </is>
       </c>
       <c r="B2434" t="inlineStr">
@@ -86409,7 +86409,7 @@
       </c>
       <c r="D2434" t="inlineStr">
         <is>
-          <t>Lafran莽aise</t>
+          <t>Lafrançaise</t>
         </is>
       </c>
       <c r="E2434"/>
@@ -87914,7 +87914,7 @@
     <row r="2474">
       <c r="A2474" t="inlineStr">
         <is>
-          <t>Saint-脡tienne-de-Tulmont (Tarn-et-Garonne, France)</t>
+          <t>Saint-Étienne-de-Tulmont (Tarn-et-Garonne, France)</t>
         </is>
       </c>
       <c r="B2474" t="inlineStr">
@@ -87929,7 +87929,7 @@
       </c>
       <c r="D2474" t="inlineStr">
         <is>
-          <t>Saint-脡tienne-de-Tulmont</t>
+          <t>Saint-Étienne-de-Tulmont</t>
         </is>
       </c>
       <c r="E2474"/>
@@ -88446,7 +88446,7 @@
     <row r="2488">
       <c r="A2488" t="inlineStr">
         <is>
-          <t>Va茂ssac (Tarn-et-Garonne, France)</t>
+          <t>Vaïssac (Tarn-et-Garonne, France)</t>
         </is>
       </c>
       <c r="B2488" t="inlineStr">
@@ -88461,7 +88461,7 @@
       </c>
       <c r="D2488" t="inlineStr">
         <is>
-          <t>Va茂ssac</t>
+          <t>Vaïssac</t>
         </is>
       </c>
       <c r="E2488"/>
@@ -88826,7 +88826,7 @@
     <row r="2498">
       <c r="A2498" t="inlineStr">
         <is>
-          <t>Mont-de-Randon (Lozère, France)</t>
+          <t>Monts-de-Randon (Lozère, France)</t>
         </is>
       </c>
       <c r="B2498" t="inlineStr">
@@ -88841,7 +88841,7 @@
       </c>
       <c r="D2498" t="inlineStr">
         <is>
-          <t>Mont-de-Randon</t>
+          <t>Monts-de-Randon</t>
         </is>
       </c>
       <c r="E2498"/>
